--- a/data/trans_dic/P2A_enfcro_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P2A_enfcro_R-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con enfermedades crónicas</t>
+          <t>Hogares con personas con enfermedades crónicas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>42,07; 49,61</t>
+          <t>41,97; 49,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>55,39; 62,81</t>
+          <t>55,08; 62,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46,62; 54,61</t>
+          <t>46,74; 54,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34,44; 43,05</t>
+          <t>34,83; 43,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>56,06; 63,23</t>
+          <t>55,92; 63,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,62; 71,35</t>
+          <t>63,83; 71,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,22; 65,6</t>
+          <t>58,42; 66,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>30,73; 44,84</t>
+          <t>31,63; 44,73</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>50,09; 55,3</t>
+          <t>50,16; 55,39</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>60,79; 65,99</t>
+          <t>60,8; 66,17</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>53,89; 59,16</t>
+          <t>53,68; 59,22</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>34,89; 42,53</t>
+          <t>34,89; 42,6</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>42,25; 48,68</t>
+          <t>41,78; 48,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>49,04; 55,5</t>
+          <t>48,95; 55,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45,34; 51,86</t>
+          <t>45,75; 52,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,62; 37,01</t>
+          <t>13,3; 36,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>59,2; 65,28</t>
+          <t>58,58; 65,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>66,02; 72,05</t>
+          <t>65,76; 71,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,92; 66,8</t>
+          <t>60,69; 66,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>40,81; 46,35</t>
+          <t>40,91; 46,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>51,61; 56,3</t>
+          <t>51,42; 56,13</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>58,2; 62,86</t>
+          <t>58,26; 62,67</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54,26; 58,74</t>
+          <t>54,28; 58,67</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>23,13; 40,54</t>
+          <t>23,39; 40,53</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>40,84; 48,6</t>
+          <t>41,01; 48,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>44,87; 52,49</t>
+          <t>44,94; 52,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>43,21; 50,64</t>
+          <t>43,05; 50,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27,91; 36,38</t>
+          <t>28,43; 36,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>56,42; 63,98</t>
+          <t>56,4; 63,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>62,64; 69,53</t>
+          <t>62,81; 69,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>54,51; 62,05</t>
+          <t>54,51; 61,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>33,13; 72,06</t>
+          <t>32,67; 73,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>49,79; 55,36</t>
+          <t>49,9; 55,28</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>55,02; 60,15</t>
+          <t>55,3; 60,4</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>50,15; 55,32</t>
+          <t>49,95; 55,07</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>32,42; 61,41</t>
+          <t>32,2; 60,29</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>39,07; 45,49</t>
+          <t>39,16; 45,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>52,65; 59,34</t>
+          <t>52,39; 59,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>49,03; 55,41</t>
+          <t>49,0; 55,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28,15; 35,07</t>
+          <t>28,59; 35,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>56,49; 62,65</t>
+          <t>55,97; 62,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,16; 70,0</t>
+          <t>63,82; 69,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,14; 63,2</t>
+          <t>57,15; 63,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>29,43; 39,53</t>
+          <t>29,3; 39,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>48,88; 53,52</t>
+          <t>48,79; 53,32</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59,63; 63,85</t>
+          <t>59,37; 63,87</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>54,36; 58,88</t>
+          <t>54,21; 58,6</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30,02; 36,38</t>
+          <t>29,83; 36,49</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>42,58; 46,34</t>
+          <t>42,58; 46,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>52,23; 55,7</t>
+          <t>52,17; 55,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47,97; 51,55</t>
+          <t>48,0; 51,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25,38; 35,18</t>
+          <t>24,61; 35,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>58,74; 62,17</t>
+          <t>58,8; 62,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>65,95; 69,23</t>
+          <t>65,88; 69,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>59,63; 62,93</t>
+          <t>59,8; 62,99</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>38,18; 53,57</t>
+          <t>38,04; 53,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>51,27; 53,79</t>
+          <t>51,26; 53,76</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59,7; 62,11</t>
+          <t>59,72; 62,11</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54,38; 56,82</t>
+          <t>54,42; 56,76</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>33,68; 42,82</t>
+          <t>33,86; 42,62</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con enfermedades crónicas</t>
+          <t>Hogares con personas con enfermedades crónicas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>291993; 344265</t>
+          <t>291277; 345715</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>389620; 441818</t>
+          <t>387461; 442132</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>314584; 368477</t>
+          <t>315396; 369731</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>218837; 273584</t>
+          <t>221322; 274297</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>385870; 435260</t>
+          <t>384938; 436487</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>443469; 497373</t>
+          <t>444909; 496355</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>391725; 441409</t>
+          <t>393087; 444717</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>222863; 325222</t>
+          <t>229429; 324460</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>692446; 764398</t>
+          <t>693394; 765634</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>851424; 924243</t>
+          <t>851502; 926662</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>726308; 797293</t>
+          <t>723355; 798079</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>474779; 578712</t>
+          <t>474758; 579718</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>406340; 468230</t>
+          <t>401856; 465399</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>499227; 564943</t>
+          <t>498279; 563668</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>463531; 530239</t>
+          <t>467785; 532043</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>186341; 441454</t>
+          <t>158613; 439824</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>573297; 632124</t>
+          <t>567251; 632703</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>681431; 743672</t>
+          <t>678813; 741859</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>635362; 696662</t>
+          <t>632939; 696624</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>391244; 444307</t>
+          <t>392196; 448576</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>996155; 1086634</t>
+          <t>992583; 1083421</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1193231; 1288630</t>
+          <t>1194307; 1284820</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1120671; 1213261</t>
+          <t>1121159; 1211649</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>497622; 872290</t>
+          <t>503331; 871923</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>277103; 329783</t>
+          <t>278236; 330386</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>339934; 397702</t>
+          <t>340442; 398741</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>328220; 384663</t>
+          <t>327006; 386062</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>196693; 256363</t>
+          <t>200342; 255804</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>385848; 437556</t>
+          <t>385675; 436721</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>486857; 540365</t>
+          <t>488128; 541161</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>427914; 487071</t>
+          <t>427886; 485175</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>309180; 672558</t>
+          <t>304905; 686321</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>678326; 754186</t>
+          <t>679814; 753109</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>844434; 923144</t>
+          <t>848785; 927005</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>774614; 854445</t>
+          <t>771581; 850539</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>531068; 1005974</t>
+          <t>527521; 987551</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>368121; 428598</t>
+          <t>368974; 427055</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>499005; 562378</t>
+          <t>496530; 559847</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>459711; 519496</t>
+          <t>459407; 517461</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>260916; 325084</t>
+          <t>264998; 326689</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>586696; 650672</t>
+          <t>581298; 647003</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>674902; 736368</t>
+          <t>671280; 736171</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>596461; 659670</t>
+          <t>596512; 663359</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>322239; 432846</t>
+          <t>320853; 436712</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>968234; 1060132</t>
+          <t>966457; 1056216</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1192309; 1276745</t>
+          <t>1187286; 1277091</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1077153; 1166599</t>
+          <t>1074160; 1161134</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>606924; 735585</t>
+          <t>602999; 737660</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1395018; 1518207</t>
+          <t>1395138; 1511228</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1789667; 1908688</t>
+          <t>1787734; 1905940</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1628133; 1749665</t>
+          <t>1629433; 1743343</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>878030; 1217031</t>
+          <t>851461; 1212100</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1984896; 2100982</t>
+          <t>1987034; 2098254</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2346785; 2463521</t>
+          <t>2344188; 2461200</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2113439; 2230684</t>
+          <t>2119804; 2232713</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1417449; 1988813</t>
+          <t>1412102; 1968520</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3412677; 3580049</t>
+          <t>3411780; 3578155</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4170243; 4338258</t>
+          <t>4171772; 4338291</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3773554; 3942718</t>
+          <t>3775991; 3938798</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2415351; 3070970</t>
+          <t>2428411; 3056824</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_enfcro_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P2A_enfcro_R-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>40,81%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>41,97; 49,81</t>
+          <t>42,02; 49,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>55,08; 62,85</t>
+          <t>54,93; 62,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46,74; 54,79</t>
+          <t>46,66; 54,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34,83; 43,17</t>
+          <t>33,96; 41,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>55,92; 63,41</t>
+          <t>56,08; 63,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,83; 71,21</t>
+          <t>64,0; 71,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,42; 66,1</t>
+          <t>58,53; 66,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>31,63; 44,73</t>
+          <t>40,76; 46,9</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>50,16; 55,39</t>
+          <t>49,91; 55,25</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>60,8; 66,17</t>
+          <t>60,98; 66,17</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>53,68; 59,22</t>
+          <t>53,45; 58,77</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>34,89; 42,6</t>
+          <t>38,47; 43,3</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>39,01%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>41,78; 48,39</t>
+          <t>41,95; 48,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>48,95; 55,37</t>
+          <t>49,08; 55,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45,75; 52,04</t>
+          <t>45,89; 52,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,3; 36,87</t>
+          <t>31,62; 38,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>58,58; 65,34</t>
+          <t>59,1; 65,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>65,76; 71,87</t>
+          <t>65,56; 71,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,69; 66,8</t>
+          <t>60,51; 66,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>40,91; 46,79</t>
+          <t>40,76; 45,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>51,42; 56,13</t>
+          <t>51,6; 56,21</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>58,26; 62,67</t>
+          <t>58,23; 62,68</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54,28; 58,67</t>
+          <t>54,08; 58,43</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>23,39; 40,53</t>
+          <t>36,96; 41,02</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>32,36%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>41,01; 48,69</t>
+          <t>40,76; 48,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>44,94; 52,63</t>
+          <t>44,81; 52,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>43,05; 50,83</t>
+          <t>42,7; 50,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>28,43; 36,3</t>
+          <t>27,01; 34,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>56,4; 63,86</t>
+          <t>56,58; 63,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>62,81; 69,63</t>
+          <t>62,6; 69,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>54,51; 61,8</t>
+          <t>54,57; 61,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>32,67; 73,53</t>
+          <t>31,02; 37,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>49,9; 55,28</t>
+          <t>49,72; 55,32</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>55,3; 60,4</t>
+          <t>54,91; 60,32</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>49,95; 55,07</t>
+          <t>49,83; 55,14</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>32,2; 60,29</t>
+          <t>30,18; 35,13</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>33,86%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>39,16; 45,32</t>
+          <t>38,9; 45,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>52,39; 59,07</t>
+          <t>52,58; 59,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>49,0; 55,19</t>
+          <t>49,19; 55,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28,59; 35,25</t>
+          <t>26,94; 33,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>55,97; 62,29</t>
+          <t>56,13; 62,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,82; 69,98</t>
+          <t>63,87; 69,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,15; 63,55</t>
+          <t>57,4; 63,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>29,3; 39,88</t>
+          <t>35,0; 39,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>48,79; 53,32</t>
+          <t>48,96; 53,31</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59,37; 63,87</t>
+          <t>59,69; 63,93</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>54,21; 58,6</t>
+          <t>54,02; 58,65</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>29,83; 36,49</t>
+          <t>32,01; 35,73</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>36,39%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>42,58; 46,12</t>
+          <t>42,75; 46,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>52,17; 55,62</t>
+          <t>51,99; 55,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48,0; 51,36</t>
+          <t>47,85; 51,38</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24,61; 35,03</t>
+          <t>31,32; 34,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>58,8; 62,09</t>
+          <t>58,68; 61,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>65,88; 69,17</t>
+          <t>65,86; 69,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>59,8; 62,99</t>
+          <t>59,57; 62,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>38,04; 53,03</t>
+          <t>38,36; 41,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>51,26; 53,76</t>
+          <t>51,31; 53,76</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59,72; 62,11</t>
+          <t>59,62; 62,05</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54,42; 56,76</t>
+          <t>54,43; 56,78</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>33,86; 42,62</t>
+          <t>35,31; 37,64</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>245955</t>
+          <t>258935</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>294869</t>
+          <t>322543</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>540824</t>
+          <t>581477</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>291277; 345715</t>
+          <t>291617; 343784</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>387461; 442132</t>
+          <t>386390; 441268</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>315396; 369731</t>
+          <t>314857; 367144</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>221322; 274297</t>
+          <t>234587; 286334</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>384938; 436487</t>
+          <t>386046; 434078</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>444909; 496355</t>
+          <t>446081; 497351</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>393087; 444717</t>
+          <t>393800; 444546</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>229429; 324460</t>
+          <t>299220; 344324</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>693394; 765634</t>
+          <t>689937; 763720</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>851502; 926662</t>
+          <t>854057; 926725</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>723355; 798079</t>
+          <t>720327; 792005</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>474758; 579718</t>
+          <t>548158; 616930</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>340314</t>
+          <t>363682</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>419659</t>
+          <t>463475</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>759973</t>
+          <t>827157</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>401856; 465399</t>
+          <t>403482; 468854</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>498279; 563668</t>
+          <t>499632; 566444</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>467785; 532043</t>
+          <t>469227; 533846</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>158613; 439824</t>
+          <t>331678; 399555</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>567251; 632703</t>
+          <t>572298; 633951</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>678813; 741859</t>
+          <t>676691; 741099</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>632939; 696624</t>
+          <t>631068; 694210</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>392196; 448576</t>
+          <t>436776; 490668</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>992583; 1083421</t>
+          <t>996018; 1084979</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1194307; 1284820</t>
+          <t>1193837; 1285118</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1121159; 1211649</t>
+          <t>1117018; 1206753</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>503331; 871923</t>
+          <t>783718; 869733</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>225601</t>
+          <t>244739</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>454826</t>
+          <t>277957</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>680426</t>
+          <t>522696</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>278236; 330386</t>
+          <t>276565; 332029</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>340442; 398741</t>
+          <t>339472; 398963</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>327006; 386062</t>
+          <t>324309; 386525</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>200342; 255804</t>
+          <t>216931; 277649</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>385675; 436721</t>
+          <t>386904; 436362</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>488128; 541161</t>
+          <t>486536; 540613</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>427886; 485175</t>
+          <t>428375; 486476</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>304905; 686321</t>
+          <t>251935; 300861</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>679814; 753109</t>
+          <t>677312; 753613</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>848785; 927005</t>
+          <t>842687; 925810</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>771581; 850539</t>
+          <t>769716; 851599</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>527521; 987551</t>
+          <t>487502; 567426</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>292832</t>
+          <t>294644</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>395440</t>
+          <t>419550</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>688271</t>
+          <t>714194</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>368974; 427055</t>
+          <t>366545; 428482</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>496530; 559847</t>
+          <t>498359; 560687</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>459407; 517461</t>
+          <t>461182; 520045</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>264998; 326689</t>
+          <t>266732; 327584</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>581298; 647003</t>
+          <t>583005; 649828</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>671280; 736171</t>
+          <t>671897; 733506</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>596512; 663359</t>
+          <t>599147; 665567</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>320853; 436712</t>
+          <t>391631; 446915</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>966457; 1056216</t>
+          <t>969836; 1056016</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1187286; 1277091</t>
+          <t>1193559; 1278340</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1074160; 1161134</t>
+          <t>1070297; 1162090</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>602999; 737660</t>
+          <t>675105; 753665</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1104702</t>
+          <t>1162000</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1564793</t>
+          <t>1483525</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2669494</t>
+          <t>2645524</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1395138; 1511228</t>
+          <t>1400719; 1511926</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1787734; 1905940</t>
+          <t>1781529; 1911230</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1629433; 1743343</t>
+          <t>1624172; 1744035</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>851461; 1212100</t>
+          <t>1106345; 1221352</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1987034; 2098254</t>
+          <t>1983020; 2093417</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2344188; 2461200</t>
+          <t>2343467; 2459148</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2119804; 2232713</t>
+          <t>2111362; 2229526</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1412102; 1968520</t>
+          <t>1433536; 1533086</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3411780; 3578155</t>
+          <t>3414949; 3578136</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4171772; 4338291</t>
+          <t>4164479; 4334381</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3775991; 3938798</t>
+          <t>3777097; 3939736</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2428411; 3056824</t>
+          <t>2567115; 2736520</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_enfcro_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P2A_enfcro_R-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con enfermedades crónicas (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con enfermedades crónicas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con enfermedades crónicas (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con enfermedades crónicas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
